--- a/BDP_Minatitlan.xlsx
+++ b/BDP_Minatitlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/molina/PycharmProjects/tecnm/workspaces/prodep/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855D46A1-ECCF-C340-B54A-9669E3B9B32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6555E7E5-6974-C94E-9241-6F179191B65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="145">
   <si>
     <t>Diagnóstico Socioeconómico, Educativo y Ambiental — Minatitlán, Ver. (2020–2026)</t>
   </si>
@@ -477,6 +477,9 @@
     <t>Molina Gomez, Kevin David
 Instituto Tecnológico de Minatitlán — TecNM
 ORCID: https://orcid.org/0009-0009-3099-6893</t>
+  </si>
+  <si>
+    <t>https://github.com/tec-mina/bdp_minatitlan.git</t>
   </si>
 </sst>
 </file>
@@ -495,22 +498,26 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF003366"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -585,13 +592,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -902,10 +909,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
+      <c r="B1" s="8"/>
     </row>
     <row r="2" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -919,7 +926,7 @@
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>143</v>
       </c>
     </row>
@@ -951,7 +958,9 @@
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="8" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
